--- a/questionnaire_templates/018_pcos_health_assessment_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/018_pcos_health_assessment_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -914,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hair_loss</t>
+          <t>skin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hair Loss</t>
+          <t>Skin</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>skin</t>
+          <t>vaginal_discharge</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>Vaginal discharge</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>skin</t>
+          <t>vulvarian_cysts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>Vulvarian cysts</t>
         </is>
       </c>
     </row>
@@ -1270,214 +1270,95 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>skin</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>symptom_frequency_choices</t>
+          <t>family_history_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>skin</t>
+          <t>mother_(pcos/pcod)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>Mother (PCOS/PCOD)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>symptom_frequency_choices</t>
+          <t>family_history_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>vaginal_discharge</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vaginal discharge</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>symptom_frequency_choices</t>
+          <t>family_history_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>vulvarian_cysts</t>
+          <t>mother_(polycystic_ovary_syndrome_(pcos))</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vulvarian cysts</t>
+          <t>Mother (Polycystic ovary syndrome (PCOS))</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>symptom_frequency_choices</t>
+          <t>menstrual_regularity_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>family_history_choices</t>
+          <t>menstrual_regularity_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mother_(pcos/pcod)</t>
+          <t>irregular</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
-        <is>
-          <t>Mother (PCOS/PCOD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>family_history_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>father</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Father</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>family_history_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>mother_(pcos/pcod)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Mother (PCOS/PCOD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>family_history_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>father</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Father</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>family_history_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>mother_(polycystic_ovary_syndrome_(pcos))</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Mother (Polycystic ovary syndrome (PCOS))</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>menstrual_regularity_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>menstrual_regularity_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>irregular</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Irregular</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>menstrual_regularity_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>irregular</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>Irregular</t>
         </is>
